--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЙ РЕНТС ООД/СКАЙ РЕНТС ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЙ РЕНТС ООД/СКАЙ РЕНТС ООД.xlsx
@@ -247,7 +247,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1490,7 +1490,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="7">
-        <v>1.6174</v>
+        <v>1.617405</v>
       </c>
       <c r="E23" s="6">
         <v>912.75</v>
@@ -1510,7 +1510,7 @@
         <v>2</v>
       </c>
       <c r="D24" s="7">
-        <v>2.01</v>
+        <v>2.010034</v>
       </c>
       <c r="E24" s="6">
         <v>334.53</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЙ РЕНТС ООД/СКАЙ РЕНТС ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЙ РЕНТС ООД/СКАЙ РЕНТС ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="76">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -638,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -651,13 +654,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -700,116 +703,125 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>79.76000000000001</v>
+        <v>79.762</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2">
-        <v>1.54</v>
+        <v>1.499</v>
       </c>
       <c r="I2" s="1">
-        <v>122.83</v>
+        <v>1.539</v>
       </c>
       <c r="J2">
+        <v>122.753718</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.64</v>
       </c>
-      <c r="K2" s="1">
-        <v>130.81</v>
-      </c>
-      <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>130.80968</v>
+      </c>
+      <c r="M2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>65.23</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3">
-        <v>1.54</v>
+        <v>1.499</v>
       </c>
       <c r="I3" s="1">
-        <v>100.45</v>
+        <v>1.539</v>
       </c>
       <c r="J3">
+        <v>100.38897</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.61</v>
       </c>
-      <c r="K3" s="1">
-        <v>105.02</v>
-      </c>
-      <c r="L3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>105.0203</v>
+      </c>
+      <c r="M3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H4">
         <v>1.63</v>
@@ -823,37 +835,40 @@
       <c r="K4" s="1">
         <v>1.63</v>
       </c>
-      <c r="L4" t="s">
-        <v>44</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="M4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H5">
         <v>0.97</v>
@@ -867,169 +882,181 @@
       <c r="K5" s="1">
         <v>0.97</v>
       </c>
-      <c r="L5" t="s">
-        <v>44</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="M5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6">
+        <v>96.369</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6">
+        <v>1.499</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.539</v>
+      </c>
+      <c r="J6">
+        <v>148.311891</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="L6" s="1">
+        <v>154.1904</v>
+      </c>
+      <c r="M6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7">
+        <v>64.161</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7">
+        <v>1.546</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.576</v>
+      </c>
+      <c r="J7">
+        <v>101.117736</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L7" s="1">
+        <v>107.79048</v>
+      </c>
+      <c r="M7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6">
-        <v>96.37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6">
-        <v>1.54</v>
-      </c>
-      <c r="I6" s="1">
-        <v>148.41</v>
-      </c>
-      <c r="J6">
-        <v>1.6</v>
-      </c>
-      <c r="K6" s="1">
-        <v>154.19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>45</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>30</v>
       </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7">
-        <v>64.16</v>
-      </c>
-      <c r="G7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7">
-        <v>1.58</v>
-      </c>
-      <c r="I7" s="1">
-        <v>101.37</v>
-      </c>
-      <c r="J7">
-        <v>1.68</v>
-      </c>
-      <c r="K7" s="1">
-        <v>107.79</v>
-      </c>
-      <c r="L7" t="s">
-        <v>46</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>80.56999999999999</v>
+        <v>80.572</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8">
         <v>2.01</v>
       </c>
       <c r="I8" s="1">
-        <v>161.95</v>
+        <v>2.01</v>
       </c>
       <c r="J8">
+        <v>161.94972</v>
+      </c>
+      <c r="K8" s="1">
         <v>2.01</v>
       </c>
-      <c r="K8" s="1">
-        <v>161.95</v>
-      </c>
-      <c r="L8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M8">
+      <c r="L8" s="1">
+        <v>161.94972</v>
+      </c>
+      <c r="M8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H9">
         <v>2.3</v>
@@ -1043,81 +1070,87 @@
       <c r="K9" s="1">
         <v>2.3</v>
       </c>
-      <c r="L9" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="1">
+        <v>2.3</v>
+      </c>
+      <c r="M9" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>65.86</v>
+        <v>65.863</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H10">
-        <v>1.68</v>
+        <v>1.653</v>
       </c>
       <c r="I10" s="1">
-        <v>110.64</v>
+        <v>1.683</v>
       </c>
       <c r="J10">
+        <v>110.847429</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.75</v>
       </c>
-      <c r="K10" s="1">
-        <v>115.26</v>
-      </c>
-      <c r="L10" t="s">
-        <v>49</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="1">
+        <v>115.26025</v>
+      </c>
+      <c r="M10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H11">
         <v>1.11</v>
@@ -1131,37 +1164,40 @@
       <c r="K11" s="1">
         <v>1.11</v>
       </c>
-      <c r="L11" t="s">
-        <v>49</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="1">
+        <v>1.11</v>
+      </c>
+      <c r="M11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12">
         <v>2.64</v>
@@ -1175,169 +1211,181 @@
       <c r="K12" s="1">
         <v>2.64</v>
       </c>
-      <c r="L12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M12">
+      <c r="L12" s="1">
+        <v>2.64</v>
+      </c>
+      <c r="M12" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12">
         <v>0</v>
       </c>
-      <c r="N12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>70.58</v>
+        <v>70.581</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H13">
-        <v>1.68</v>
+        <v>1.653</v>
       </c>
       <c r="I13" s="1">
-        <v>118.57</v>
+        <v>1.683</v>
       </c>
       <c r="J13">
+        <v>118.787823</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.79</v>
       </c>
-      <c r="K13" s="1">
-        <v>126.34</v>
-      </c>
-      <c r="L13" t="s">
-        <v>50</v>
-      </c>
-      <c r="M13">
+      <c r="L13" s="1">
+        <v>126.33999</v>
+      </c>
+      <c r="M13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13">
         <v>0</v>
       </c>
-      <c r="N13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F14">
-        <v>85.86</v>
+        <v>85.861</v>
       </c>
       <c r="G14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H14">
         <v>2.01</v>
       </c>
       <c r="I14" s="1">
-        <v>172.58</v>
+        <v>2.01</v>
       </c>
       <c r="J14">
+        <v>172.58061</v>
+      </c>
+      <c r="K14" s="1">
         <v>2.01</v>
       </c>
-      <c r="K14" s="1">
-        <v>172.58</v>
-      </c>
-      <c r="L14" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14">
+      <c r="L14" s="1">
+        <v>172.58061</v>
+      </c>
+      <c r="M14" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14">
         <v>0</v>
       </c>
-      <c r="N14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15">
-        <v>41.55</v>
+        <v>41.547</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H15">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I15" s="1">
-        <v>71.47</v>
+        <v>1.719</v>
       </c>
       <c r="J15">
+        <v>71.419293</v>
+      </c>
+      <c r="K15" s="1">
         <v>1.79</v>
       </c>
-      <c r="K15" s="1">
-        <v>74.37</v>
-      </c>
-      <c r="L15" t="s">
-        <v>52</v>
-      </c>
-      <c r="M15">
+      <c r="L15" s="1">
+        <v>74.36913</v>
+      </c>
+      <c r="M15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N15">
         <v>0</v>
       </c>
-      <c r="N15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H16">
         <v>2.04</v>
@@ -1351,37 +1399,40 @@
       <c r="K16" s="1">
         <v>2.04</v>
       </c>
-      <c r="L16" t="s">
-        <v>53</v>
-      </c>
-      <c r="M16">
+      <c r="L16" s="1">
+        <v>2.04</v>
+      </c>
+      <c r="M16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16">
         <v>0</v>
       </c>
-      <c r="N16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H17">
         <v>1.78</v>
@@ -1395,63 +1446,69 @@
       <c r="K17" s="1">
         <v>1.78</v>
       </c>
-      <c r="L17" t="s">
-        <v>53</v>
-      </c>
-      <c r="M17">
+      <c r="L17" s="1">
+        <v>1.78</v>
+      </c>
+      <c r="M17" t="s">
+        <v>54</v>
+      </c>
+      <c r="N17">
         <v>0</v>
       </c>
-      <c r="N17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F18">
         <v>80.81999999999999</v>
       </c>
       <c r="G18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H18">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I18" s="1">
-        <v>139.01</v>
+        <v>1.719</v>
       </c>
       <c r="J18">
+        <v>138.92958</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.78</v>
       </c>
-      <c r="K18" s="1">
-        <v>143.86</v>
-      </c>
-      <c r="L18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18">
+      <c r="L18" s="1">
+        <v>143.8596</v>
+      </c>
+      <c r="M18" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18">
         <v>0</v>
       </c>
-      <c r="N18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1459,58 +1516,58 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:15">
       <c r="A22" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="6">
-        <v>564.33</v>
+        <v>564.333</v>
       </c>
       <c r="C23" s="6">
         <v>8</v>
       </c>
       <c r="D23" s="7">
-        <v>1.617405</v>
+        <v>1.617053</v>
       </c>
       <c r="E23" s="6">
-        <v>912.75</v>
+        <v>912.5599999999999</v>
       </c>
       <c r="F23" s="6">
         <v>957.64</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:15">
       <c r="A24" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="6">
-        <v>166.43</v>
+        <v>166.433</v>
       </c>
       <c r="C24" s="6">
         <v>2</v>
       </c>
       <c r="D24" s="7">
-        <v>2.010034</v>
+        <v>2.01</v>
       </c>
       <c r="E24" s="6">
         <v>334.53</v>
@@ -1519,9 +1576,9 @@
         <v>334.53</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:15">
       <c r="A25" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B25" s="6">
         <v>1</v>
@@ -1539,9 +1596,9 @@
         <v>1.11</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:15">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="6">
         <v>1</v>
@@ -1559,9 +1616,9 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:15">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="6">
         <v>1</v>
@@ -1579,9 +1636,9 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:15">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" s="6">
         <v>1</v>
@@ -1599,9 +1656,9 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:15">
       <c r="A29" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="6">
         <v>1</v>
@@ -1619,9 +1676,9 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:15">
       <c r="A30" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="6">
         <v>1</v>
@@ -1639,9 +1696,9 @@
         <v>2.3</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:15">
       <c r="A31" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="6">
         <v>1</v>
@@ -1659,19 +1716,19 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:15">
       <c r="A32" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B32" s="9">
-        <v>737.76</v>
+        <v>737.766</v>
       </c>
       <c r="C32" s="9">
         <v>17</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="9">
-        <v>1259.75</v>
+        <v>1259.56</v>
       </c>
       <c r="F32" s="9">
         <v>1304.64</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЙ РЕНТС ООД/СКАЙ РЕНТС ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКАЙ РЕНТС ООД/СКАЙ РЕНТС ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="75">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -249,8 +246,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -343,10 +340,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -641,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -654,13 +651,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -703,125 +700,116 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>79.762</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>1.499</v>
+        <v>1.539</v>
       </c>
       <c r="I2" s="1">
-        <v>1.539</v>
+        <v>122.754</v>
       </c>
       <c r="J2">
-        <v>122.753718</v>
+        <v>1.64</v>
       </c>
       <c r="K2" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="L2" s="1">
-        <v>130.80968</v>
-      </c>
-      <c r="M2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>130.81</v>
+      </c>
+      <c r="L2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>65.23</v>
       </c>
       <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3">
+        <v>1.539</v>
+      </c>
+      <c r="I3" s="1">
+        <v>100.389</v>
+      </c>
+      <c r="J3">
+        <v>1.61</v>
+      </c>
+      <c r="K3" s="1">
+        <v>105.02</v>
+      </c>
+      <c r="L3" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
         <v>41</v>
-      </c>
-      <c r="H3">
-        <v>1.499</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.539</v>
-      </c>
-      <c r="J3">
-        <v>100.38897</v>
-      </c>
-      <c r="K3" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L3" s="1">
-        <v>105.0203</v>
-      </c>
-      <c r="M3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
       </c>
       <c r="H4">
         <v>1.63</v>
@@ -835,40 +823,37 @@
       <c r="K4" s="1">
         <v>1.63</v>
       </c>
-      <c r="L4" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="M4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="L4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H5">
         <v>0.97</v>
@@ -882,181 +867,169 @@
       <c r="K5" s="1">
         <v>0.97</v>
       </c>
-      <c r="L5" s="1">
-        <v>0.97</v>
-      </c>
-      <c r="M5" t="s">
-        <v>45</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="L5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>96.369</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H6">
-        <v>1.499</v>
+        <v>1.539</v>
       </c>
       <c r="I6" s="1">
-        <v>1.539</v>
+        <v>148.312</v>
       </c>
       <c r="J6">
-        <v>148.311891</v>
+        <v>1.6</v>
       </c>
       <c r="K6" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="L6" s="1">
-        <v>154.1904</v>
-      </c>
-      <c r="M6" t="s">
-        <v>46</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>154.19</v>
+      </c>
+      <c r="L6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
         <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
       </c>
       <c r="F7">
         <v>64.161</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H7">
-        <v>1.546</v>
+        <v>1.576</v>
       </c>
       <c r="I7" s="1">
-        <v>1.576</v>
+        <v>101.118</v>
       </c>
       <c r="J7">
-        <v>101.117736</v>
+        <v>1.68</v>
       </c>
       <c r="K7" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L7" s="1">
-        <v>107.79048</v>
-      </c>
-      <c r="M7" t="s">
-        <v>47</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>107.79</v>
+      </c>
+      <c r="L7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>80.572</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H8">
         <v>2.01</v>
       </c>
       <c r="I8" s="1">
+        <v>161.95</v>
+      </c>
+      <c r="J8">
         <v>2.01</v>
       </c>
-      <c r="J8">
-        <v>161.94972</v>
-      </c>
       <c r="K8" s="1">
-        <v>2.01</v>
-      </c>
-      <c r="L8" s="1">
-        <v>161.94972</v>
-      </c>
-      <c r="M8" t="s">
-        <v>48</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>161.95</v>
+      </c>
+      <c r="L8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H9">
         <v>2.3</v>
@@ -1070,87 +1043,81 @@
       <c r="K9" s="1">
         <v>2.3</v>
       </c>
-      <c r="L9" s="1">
-        <v>2.3</v>
-      </c>
-      <c r="M9" t="s">
-        <v>49</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="L9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F10">
         <v>65.863</v>
       </c>
       <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>1.683</v>
+      </c>
+      <c r="I10" s="1">
+        <v>110.847</v>
+      </c>
+      <c r="J10">
+        <v>1.75</v>
+      </c>
+      <c r="K10" s="1">
+        <v>115.26</v>
+      </c>
+      <c r="L10" t="s">
+        <v>49</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
         <v>41</v>
-      </c>
-      <c r="H10">
-        <v>1.653</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1.683</v>
-      </c>
-      <c r="J10">
-        <v>110.847429</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L10" s="1">
-        <v>115.26025</v>
-      </c>
-      <c r="M10" t="s">
-        <v>50</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>42</v>
       </c>
       <c r="H11">
         <v>1.11</v>
@@ -1164,40 +1131,37 @@
       <c r="K11" s="1">
         <v>1.11</v>
       </c>
-      <c r="L11" s="1">
-        <v>1.11</v>
-      </c>
-      <c r="M11" t="s">
-        <v>50</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="L11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H12">
         <v>2.64</v>
@@ -1211,181 +1175,169 @@
       <c r="K12" s="1">
         <v>2.64</v>
       </c>
-      <c r="L12" s="1">
-        <v>2.64</v>
-      </c>
-      <c r="M12" t="s">
-        <v>50</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="L12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13">
         <v>70.581</v>
       </c>
       <c r="G13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H13">
-        <v>1.653</v>
+        <v>1.683</v>
       </c>
       <c r="I13" s="1">
-        <v>1.683</v>
+        <v>118.788</v>
       </c>
       <c r="J13">
-        <v>118.787823</v>
+        <v>1.79</v>
       </c>
       <c r="K13" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L13" s="1">
-        <v>126.33999</v>
-      </c>
-      <c r="M13" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>126.34</v>
+      </c>
+      <c r="L13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F14">
         <v>85.861</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H14">
         <v>2.01</v>
       </c>
       <c r="I14" s="1">
+        <v>172.581</v>
+      </c>
+      <c r="J14">
         <v>2.01</v>
       </c>
-      <c r="J14">
-        <v>172.58061</v>
-      </c>
       <c r="K14" s="1">
-        <v>2.01</v>
-      </c>
-      <c r="L14" s="1">
-        <v>172.58061</v>
-      </c>
-      <c r="M14" t="s">
-        <v>52</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>172.581</v>
+      </c>
+      <c r="L14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15">
         <v>41.547</v>
       </c>
       <c r="G15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15">
+        <v>1.719</v>
+      </c>
+      <c r="I15" s="1">
+        <v>71.419</v>
+      </c>
+      <c r="J15">
+        <v>1.79</v>
+      </c>
+      <c r="K15" s="1">
+        <v>74.369</v>
+      </c>
+      <c r="L15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
         <v>41</v>
-      </c>
-      <c r="H15">
-        <v>1.689</v>
-      </c>
-      <c r="I15" s="1">
-        <v>1.719</v>
-      </c>
-      <c r="J15">
-        <v>71.419293</v>
-      </c>
-      <c r="K15" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L15" s="1">
-        <v>74.36913</v>
-      </c>
-      <c r="M15" t="s">
-        <v>53</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>42</v>
       </c>
       <c r="H16">
         <v>2.04</v>
@@ -1399,40 +1351,37 @@
       <c r="K16" s="1">
         <v>2.04</v>
       </c>
-      <c r="L16" s="1">
-        <v>2.04</v>
-      </c>
-      <c r="M16" t="s">
-        <v>54</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="L16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H17">
         <v>1.78</v>
@@ -1446,69 +1395,63 @@
       <c r="K17" s="1">
         <v>1.78</v>
       </c>
-      <c r="L17" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="M17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="L17" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
         <v>27</v>
       </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18">
         <v>80.81999999999999</v>
       </c>
       <c r="G18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H18">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I18" s="1">
-        <v>1.719</v>
+        <v>138.93</v>
       </c>
       <c r="J18">
-        <v>138.92958</v>
+        <v>1.78</v>
       </c>
       <c r="K18" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L18" s="1">
-        <v>143.8596</v>
-      </c>
-      <c r="M18" t="s">
-        <v>55</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
+        <v>143.86</v>
+      </c>
+      <c r="L18" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="3" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1516,209 +1459,209 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:14">
       <c r="A22" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="E22" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="6">
         <v>564.333</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="7">
         <v>8</v>
       </c>
       <c r="D23" s="7">
-        <v>1.617053</v>
-      </c>
-      <c r="E23" s="6">
-        <v>912.5599999999999</v>
-      </c>
-      <c r="F23" s="6">
-        <v>957.64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>1.617</v>
+      </c>
+      <c r="E23" s="7">
+        <v>912.557</v>
+      </c>
+      <c r="F23" s="7">
+        <v>957.639</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="6">
         <v>166.433</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="7">
         <v>2</v>
       </c>
       <c r="D24" s="7">
         <v>2.01</v>
       </c>
-      <c r="E24" s="6">
-        <v>334.53</v>
-      </c>
-      <c r="F24" s="6">
-        <v>334.53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="E24" s="7">
+        <v>334.531</v>
+      </c>
+      <c r="F24" s="7">
+        <v>334.531</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="6">
         <v>1</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="7">
         <v>1</v>
       </c>
       <c r="D25" s="7">
         <v>1.11</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="7">
         <v>1.11</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="7">
         <v>1.11</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:14">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="6">
         <v>1</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="7">
         <v>1</v>
       </c>
       <c r="D26" s="7">
         <v>2.64</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="7">
         <v>2.64</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="7">
         <v>2.64</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:14">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="6">
         <v>1</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="7">
         <v>1</v>
       </c>
       <c r="D27" s="7">
         <v>2.04</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="7">
         <v>2.04</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="7">
         <v>2.04</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:14">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="6">
         <v>1</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="7">
         <v>1</v>
       </c>
       <c r="D28" s="7">
         <v>1.78</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="7">
         <v>1.78</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="7">
         <v>1.78</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:14">
       <c r="A29" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="6">
         <v>1</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="7">
         <v>1</v>
       </c>
       <c r="D29" s="7">
         <v>0.97</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="7">
         <v>0.97</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="7">
         <v>0.97</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:14">
       <c r="A30" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="6">
         <v>1</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="7">
         <v>1</v>
       </c>
       <c r="D30" s="7">
         <v>2.3</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="7">
         <v>2.3</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="7">
         <v>2.3</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:14">
       <c r="A31" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" s="6">
         <v>1</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="7">
         <v>1</v>
       </c>
       <c r="D31" s="7">
         <v>1.63</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="7">
         <v>1.63</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="7">
         <v>1.63</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:14">
       <c r="A32" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B32" s="9">
         <v>737.766</v>
@@ -1728,7 +1671,7 @@
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="9">
-        <v>1259.56</v>
+        <v>1259.558</v>
       </c>
       <c r="F32" s="9">
         <v>1304.64</v>
